--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_利用回数が0のままの件_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_利用回数が0のままの件_20260928.xlsx
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>6,000円台（当方6,095円）</t>
+          <t>6,000円台（当方6,048円）</t>
         </is>
       </c>
     </row>
